--- a/analyst/Ines/rmonize/data_proc_elem/DPE_CARLA_INES.xlsx
+++ b/analyst/Ines/rmonize/data_proc_elem/DPE_CARLA_INES.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71382071-1CE5-4AE1-877D-C7DD082354C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD25DD76-19CC-4BDF-87AE-77598DEC602B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="121">
   <si>
     <t>index</t>
   </si>
@@ -380,6 +385,9 @@
   </si>
   <si>
     <t>mk;mna</t>
+  </si>
+  <si>
+    <t>mna*1000</t>
   </si>
 </sst>
 </file>
@@ -505,8 +513,8 @@
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -522,9 +530,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -562,9 +570,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -597,26 +605,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -649,26 +640,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -843,7 +817,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L48"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="34.85546875" customWidth="1"/>
     <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
@@ -1897,10 +1871,10 @@
         <v>115</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="I35" s="9"/>
       <c r="J35" s="9" t="s">
